--- a/research/traditional_assets/database/data/malaysia/malaysia_aerospace_defense.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_aerospace_defense.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0897</v>
+        <v>-0.294</v>
       </c>
       <c r="G2">
-        <v>-0.4665922920892495</v>
+        <v>-0.00618320610687023</v>
       </c>
       <c r="H2">
-        <v>-0.4746450304259635</v>
+        <v>-0.01461832061068702</v>
       </c>
       <c r="I2">
-        <v>-0.3711967545638946</v>
+        <v>-0.1423664122137405</v>
       </c>
       <c r="J2">
-        <v>-0.3711967545638946</v>
+        <v>-0.1423664122137405</v>
       </c>
       <c r="K2">
-        <v>-38.5</v>
+        <v>-0.371</v>
       </c>
       <c r="L2">
-        <v>-0.7809330628803246</v>
+        <v>-0.01416030534351145</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>6.27</v>
+        <v>1.53</v>
       </c>
       <c r="V2">
-        <v>0.08720445062586925</v>
+        <v>0.05032894736842106</v>
       </c>
       <c r="W2">
-        <v>-0.603448275862069</v>
+        <v>-0.009661458333333334</v>
       </c>
       <c r="X2">
-        <v>0.08782710006483278</v>
+        <v>0.1331197772668581</v>
       </c>
       <c r="Y2">
-        <v>-0.6912753759269017</v>
+        <v>-0.1427812356001915</v>
       </c>
       <c r="Z2">
-        <v>0.515744324720159</v>
+        <v>0.461024106985747</v>
       </c>
       <c r="AA2">
-        <v>-0.1914426195208704</v>
+        <v>-0.06563434805560443</v>
       </c>
       <c r="AB2">
-        <v>0.07278836170392965</v>
+        <v>0.1226426461925323</v>
       </c>
       <c r="AC2">
-        <v>-0.2642309812248</v>
+        <v>-0.1882769942481367</v>
       </c>
       <c r="AD2">
-        <v>24.7</v>
+        <v>4.57</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>24.7</v>
+        <v>4.57</v>
       </c>
       <c r="AG2">
-        <v>18.43</v>
+        <v>3.04</v>
       </c>
       <c r="AH2">
-        <v>0.2556935817805382</v>
+        <v>0.130683442951101</v>
       </c>
       <c r="AI2">
-        <v>0.393312101910828</v>
+        <v>0.1213166976373772</v>
       </c>
       <c r="AJ2">
-        <v>0.2040296689914757</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AK2">
-        <v>0.3260215814611711</v>
+        <v>0.08411732152739347</v>
       </c>
       <c r="AL2">
-        <v>2.21</v>
+        <v>1.03</v>
       </c>
       <c r="AM2">
-        <v>2.21</v>
+        <v>1.03</v>
       </c>
       <c r="AN2">
-        <v>-1.487951807228916</v>
+        <v>-1.904166666666667</v>
       </c>
       <c r="AO2">
-        <v>-8.28054298642534</v>
+        <v>-3.621359223300971</v>
       </c>
       <c r="AP2">
-        <v>-1.110240963855422</v>
+        <v>-1.266666666666667</v>
       </c>
       <c r="AQ2">
-        <v>-8.28054298642534</v>
+        <v>-3.621359223300971</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0897</v>
+        <v>-0.294</v>
       </c>
       <c r="G3">
-        <v>-0.4665922920892495</v>
+        <v>-0.00618320610687023</v>
       </c>
       <c r="H3">
-        <v>-0.4746450304259635</v>
+        <v>-0.01461832061068702</v>
       </c>
       <c r="I3">
-        <v>-0.3711967545638946</v>
+        <v>-0.1423664122137405</v>
       </c>
       <c r="J3">
-        <v>-0.3711967545638946</v>
+        <v>-0.1423664122137405</v>
       </c>
       <c r="K3">
-        <v>-38.5</v>
+        <v>-0.371</v>
       </c>
       <c r="L3">
-        <v>-0.7809330628803246</v>
+        <v>-0.01416030534351145</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>6.27</v>
+        <v>1.53</v>
       </c>
       <c r="V3">
-        <v>0.08720445062586925</v>
+        <v>0.05032894736842106</v>
       </c>
       <c r="W3">
-        <v>-0.603448275862069</v>
+        <v>-0.009661458333333334</v>
       </c>
       <c r="X3">
-        <v>0.08782710006483278</v>
+        <v>0.1331197772668581</v>
       </c>
       <c r="Y3">
-        <v>-0.6912753759269017</v>
+        <v>-0.1427812356001915</v>
       </c>
       <c r="Z3">
-        <v>0.515744324720159</v>
+        <v>0.461024106985747</v>
       </c>
       <c r="AA3">
-        <v>-0.1914426195208704</v>
+        <v>-0.06563434805560443</v>
       </c>
       <c r="AB3">
-        <v>0.07278836170392965</v>
+        <v>0.1226426461925323</v>
       </c>
       <c r="AC3">
-        <v>-0.2642309812248</v>
+        <v>-0.1882769942481367</v>
       </c>
       <c r="AD3">
-        <v>24.7</v>
+        <v>4.57</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>24.7</v>
+        <v>4.57</v>
       </c>
       <c r="AG3">
-        <v>18.43</v>
+        <v>3.04</v>
       </c>
       <c r="AH3">
-        <v>0.2556935817805382</v>
+        <v>0.130683442951101</v>
       </c>
       <c r="AI3">
-        <v>0.393312101910828</v>
+        <v>0.1213166976373772</v>
       </c>
       <c r="AJ3">
-        <v>0.2040296689914757</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AK3">
-        <v>0.3260215814611711</v>
+        <v>0.08411732152739347</v>
       </c>
       <c r="AL3">
-        <v>2.21</v>
+        <v>1.03</v>
       </c>
       <c r="AM3">
-        <v>2.21</v>
+        <v>1.03</v>
       </c>
       <c r="AN3">
-        <v>-1.487951807228916</v>
+        <v>-1.904166666666667</v>
       </c>
       <c r="AO3">
-        <v>-8.28054298642534</v>
+        <v>-3.621359223300971</v>
       </c>
       <c r="AP3">
-        <v>-1.110240963855422</v>
+        <v>-1.266666666666667</v>
       </c>
       <c r="AQ3">
-        <v>-8.28054298642534</v>
+        <v>-3.621359223300971</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/malaysia/malaysia_aerospace_defense.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_aerospace_defense.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.294</v>
+        <v>-0.152</v>
       </c>
       <c r="G2">
-        <v>-0.00618320610687023</v>
+        <v>-0.1467989417989418</v>
       </c>
       <c r="H2">
-        <v>-0.01461832061068702</v>
+        <v>-0.1521164021164021</v>
       </c>
       <c r="I2">
-        <v>-0.1423664122137405</v>
+        <v>-0.2354497354497355</v>
       </c>
       <c r="J2">
-        <v>-0.1423664122137405</v>
+        <v>-0.2354497354497355</v>
       </c>
       <c r="K2">
-        <v>-0.371</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="L2">
-        <v>-0.01416030534351145</v>
+        <v>-0.2259259259259259</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.53</v>
+        <v>2.22</v>
       </c>
       <c r="V2">
-        <v>0.05032894736842106</v>
+        <v>0.06115702479338844</v>
       </c>
       <c r="W2">
-        <v>-0.009661458333333334</v>
+        <v>-0.2549253731343283</v>
       </c>
       <c r="X2">
-        <v>0.1331197772668581</v>
+        <v>0.09922976766371006</v>
       </c>
       <c r="Y2">
-        <v>-0.1427812356001915</v>
+        <v>-0.3541551407980384</v>
       </c>
       <c r="Z2">
-        <v>0.461024106985747</v>
+        <v>1.03448275862069</v>
       </c>
       <c r="AA2">
-        <v>-0.06563434805560443</v>
+        <v>-0.2435686918445539</v>
       </c>
       <c r="AB2">
-        <v>0.1226426461925323</v>
+        <v>0.09507906507097338</v>
       </c>
       <c r="AC2">
-        <v>-0.1882769942481367</v>
+        <v>-0.3386477569155273</v>
       </c>
       <c r="AD2">
-        <v>4.57</v>
+        <v>3.24</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4.57</v>
+        <v>3.24</v>
       </c>
       <c r="AG2">
-        <v>3.04</v>
+        <v>1.02</v>
       </c>
       <c r="AH2">
-        <v>0.130683442951101</v>
+        <v>0.0819423368740516</v>
       </c>
       <c r="AI2">
-        <v>0.1213166976373772</v>
+        <v>0.1216216216216216</v>
       </c>
       <c r="AJ2">
-        <v>0.09090909090909091</v>
+        <v>0.02733118971061093</v>
       </c>
       <c r="AK2">
-        <v>0.08411732152739347</v>
+        <v>0.04176904176904177</v>
       </c>
       <c r="AL2">
-        <v>1.03</v>
+        <v>0.34</v>
       </c>
       <c r="AM2">
-        <v>1.03</v>
+        <v>0.34</v>
       </c>
       <c r="AN2">
-        <v>-1.904166666666667</v>
+        <v>-0.4240837696335079</v>
       </c>
       <c r="AO2">
-        <v>-3.621359223300971</v>
+        <v>-26.17647058823529</v>
       </c>
       <c r="AP2">
-        <v>-1.266666666666667</v>
+        <v>-0.1335078534031414</v>
       </c>
       <c r="AQ2">
-        <v>-3.621359223300971</v>
+        <v>-26.17647058823529</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.294</v>
+        <v>-0.152</v>
       </c>
       <c r="G3">
-        <v>-0.00618320610687023</v>
+        <v>-0.1467989417989418</v>
       </c>
       <c r="H3">
-        <v>-0.01461832061068702</v>
+        <v>-0.1521164021164021</v>
       </c>
       <c r="I3">
-        <v>-0.1423664122137405</v>
+        <v>-0.2354497354497355</v>
       </c>
       <c r="J3">
-        <v>-0.1423664122137405</v>
+        <v>-0.2354497354497355</v>
       </c>
       <c r="K3">
-        <v>-0.371</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="L3">
-        <v>-0.01416030534351145</v>
+        <v>-0.2259259259259259</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.53</v>
+        <v>2.22</v>
       </c>
       <c r="V3">
-        <v>0.05032894736842106</v>
+        <v>0.06115702479338844</v>
       </c>
       <c r="W3">
-        <v>-0.009661458333333334</v>
+        <v>-0.2549253731343283</v>
       </c>
       <c r="X3">
-        <v>0.1331197772668581</v>
+        <v>0.09922976766371006</v>
       </c>
       <c r="Y3">
-        <v>-0.1427812356001915</v>
+        <v>-0.3541551407980384</v>
       </c>
       <c r="Z3">
-        <v>0.461024106985747</v>
+        <v>1.03448275862069</v>
       </c>
       <c r="AA3">
-        <v>-0.06563434805560443</v>
+        <v>-0.2435686918445539</v>
       </c>
       <c r="AB3">
-        <v>0.1226426461925323</v>
+        <v>0.09507906507097338</v>
       </c>
       <c r="AC3">
-        <v>-0.1882769942481367</v>
+        <v>-0.3386477569155273</v>
       </c>
       <c r="AD3">
-        <v>4.57</v>
+        <v>3.24</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4.57</v>
+        <v>3.24</v>
       </c>
       <c r="AG3">
-        <v>3.04</v>
+        <v>1.02</v>
       </c>
       <c r="AH3">
-        <v>0.130683442951101</v>
+        <v>0.0819423368740516</v>
       </c>
       <c r="AI3">
-        <v>0.1213166976373772</v>
+        <v>0.1216216216216216</v>
       </c>
       <c r="AJ3">
-        <v>0.09090909090909091</v>
+        <v>0.02733118971061093</v>
       </c>
       <c r="AK3">
-        <v>0.08411732152739347</v>
+        <v>0.04176904176904177</v>
       </c>
       <c r="AL3">
-        <v>1.03</v>
+        <v>0.34</v>
       </c>
       <c r="AM3">
-        <v>1.03</v>
+        <v>0.34</v>
       </c>
       <c r="AN3">
-        <v>-1.904166666666667</v>
+        <v>-0.4240837696335079</v>
       </c>
       <c r="AO3">
-        <v>-3.621359223300971</v>
+        <v>-26.17647058823529</v>
       </c>
       <c r="AP3">
-        <v>-1.266666666666667</v>
+        <v>-0.1335078534031414</v>
       </c>
       <c r="AQ3">
-        <v>-3.621359223300971</v>
+        <v>-26.17647058823529</v>
       </c>
     </row>
   </sheetData>
